--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N10_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>25.54510566515095</v>
       </c>
       <c r="E2" t="n">
-        <v>2.948995043562777</v>
+        <v>4.816186806446421</v>
       </c>
       <c r="F2" t="n">
-        <v>3.083356907029608</v>
+        <v>5.130536564134439</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>20.24043655482601</v>
       </c>
       <c r="E3" t="n">
-        <v>2.948995043562777</v>
+        <v>4.816186806446421</v>
       </c>
       <c r="F3" t="n">
-        <v>3.083356907029608</v>
+        <v>5.130536564134439</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         <v>22.18575159448398</v>
       </c>
       <c r="E4" t="n">
-        <v>2.948995043562777</v>
+        <v>4.816186806446421</v>
       </c>
       <c r="F4" t="n">
-        <v>3.083356907029608</v>
+        <v>5.130536564134439</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         <v>16.6954833312139</v>
       </c>
       <c r="E5" t="n">
-        <v>2.948995043562777</v>
+        <v>4.816186806446421</v>
       </c>
       <c r="F5" t="n">
-        <v>3.083356907029608</v>
+        <v>5.130536564134439</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -614,10 +614,10 @@
         <v>23.0799329444861</v>
       </c>
       <c r="E6" t="n">
-        <v>2.948995043562777</v>
+        <v>4.816186806446421</v>
       </c>
       <c r="F6" t="n">
-        <v>3.083356907029608</v>
+        <v>5.130536564134439</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>21.17426126398534</v>
       </c>
       <c r="E7" t="n">
-        <v>2.948995043562777</v>
+        <v>4.816186806446421</v>
       </c>
       <c r="F7" t="n">
-        <v>3.083356907029608</v>
+        <v>5.130536564134439</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -678,10 +678,10 @@
         <v>26.60407914752895</v>
       </c>
       <c r="E8" t="n">
-        <v>2.948995043562777</v>
+        <v>4.816186806446421</v>
       </c>
       <c r="F8" t="n">
-        <v>3.083356907029608</v>
+        <v>5.130536564134439</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -689,6 +689,38 @@
         </is>
       </c>
       <c r="H8" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>W0066F0002T0006Z000C1N10.png</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="n">
+        <v>10.21390444696523</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9.388005666501392</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.816186806446421</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5.130536564134439</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>T2372</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N10_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.59140265116379</v>
+        <v>4.158602930814116</v>
       </c>
       <c r="D2" t="n">
-        <v>25.54510566515095</v>
+        <v>4.151079670587029</v>
       </c>
       <c r="E2" t="n">
-        <v>4.816186806446421</v>
+        <v>0.7826303560475434</v>
       </c>
       <c r="F2" t="n">
-        <v>5.130536564134439</v>
+        <v>0.8337121916718464</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.35639530711532</v>
+        <v>3.30791423740624</v>
       </c>
       <c r="D3" t="n">
-        <v>20.24043655482601</v>
+        <v>3.289070940159227</v>
       </c>
       <c r="E3" t="n">
-        <v>4.816186806446421</v>
+        <v>0.7826303560475434</v>
       </c>
       <c r="F3" t="n">
-        <v>5.130536564134439</v>
+        <v>0.8337121916718464</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.12418754547823</v>
+        <v>3.595180476140212</v>
       </c>
       <c r="D4" t="n">
-        <v>22.18575159448398</v>
+        <v>3.605184634103646</v>
       </c>
       <c r="E4" t="n">
-        <v>4.816186806446421</v>
+        <v>0.7826303560475434</v>
       </c>
       <c r="F4" t="n">
-        <v>5.130536564134439</v>
+        <v>0.8337121916718464</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.84212850166769</v>
+        <v>2.736845881521</v>
       </c>
       <c r="D5" t="n">
-        <v>16.6954833312139</v>
+        <v>2.713016041322259</v>
       </c>
       <c r="E5" t="n">
-        <v>4.816186806446421</v>
+        <v>0.7826303560475434</v>
       </c>
       <c r="F5" t="n">
-        <v>5.130536564134439</v>
+        <v>0.8337121916718464</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.04196627396484</v>
+        <v>3.744319519519286</v>
       </c>
       <c r="D6" t="n">
-        <v>23.0799329444861</v>
+        <v>3.750489103478992</v>
       </c>
       <c r="E6" t="n">
-        <v>4.816186806446421</v>
+        <v>0.7826303560475434</v>
       </c>
       <c r="F6" t="n">
-        <v>5.130536564134439</v>
+        <v>0.8337121916718464</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>21.01023242976446</v>
+        <v>3.414162769836724</v>
       </c>
       <c r="D7" t="n">
-        <v>21.17426126398534</v>
+        <v>3.440817455397618</v>
       </c>
       <c r="E7" t="n">
-        <v>4.816186806446421</v>
+        <v>0.7826303560475434</v>
       </c>
       <c r="F7" t="n">
-        <v>5.130536564134439</v>
+        <v>0.8337121916718464</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.09295632322086</v>
+        <v>4.24010540252339</v>
       </c>
       <c r="D8" t="n">
-        <v>26.60407914752895</v>
+        <v>4.323162861473454</v>
       </c>
       <c r="E8" t="n">
-        <v>4.816186806446421</v>
+        <v>0.7826303560475434</v>
       </c>
       <c r="F8" t="n">
-        <v>5.130536564134439</v>
+        <v>0.8337121916718464</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>10.21390444696523</v>
+        <v>1.659759472631849</v>
       </c>
       <c r="D9" t="n">
-        <v>9.388005666501392</v>
+        <v>1.525550920806476</v>
       </c>
       <c r="E9" t="n">
-        <v>4.816186806446421</v>
+        <v>0.7826303560475434</v>
       </c>
       <c r="F9" t="n">
-        <v>5.130536564134439</v>
+        <v>0.8337121916718464</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
